--- a/beispiele/Lagerbestand_beispiel.xlsx
+++ b/beispiele/Lagerbestand_beispiel.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,6 +611,110 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Elf Bar Pot Blue Razz Lemonade</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Vape</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>14</v>
+      </c>
+      <c r="D10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Großhandel</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Elf Bar Pot Watermelon</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Vape</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Großhandel</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ELF BAR POTS Kiwi Passionfruit</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vape</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Großhandel</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Elfbar Pot Cola</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vape</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Großhandel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/beispiele/Lagerbestand_beispiel.xlsx
+++ b/beispiele/Lagerbestand_beispiel.xlsx
@@ -413,306 +413,374 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Lagerbestand Automaten</t>
+          <t>ProVend — Bestand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reihenfolge = Bestückung Automat; Produkte ohne Selektor sind nicht im Automaten.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Selektor GL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nr.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Artikel</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Kategorie</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bestand</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mindestbestand</t>
+          <t>Menge Lager</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gebinde (Stk.)</t>
+          <t>Menge Automat A</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lieferant</t>
+          <t>Menge Automat B</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gesamt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Coca-Cola 0,33l Dose</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Getränke</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>240</v>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sprite 0,33l</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Selgros</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fanta 0,33l Dose</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Getränke</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>96</v>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fanta Orange 0,33l</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Selgros</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Snickers 50g</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Süßwaren</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>60</v>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Snickers Riegel 50gr.</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Selgros</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Haribo Goldbären 100g</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Süßwaren</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>45</v>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>58</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Haribo Goldbären</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Rewe</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Red Bull 0,25l</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Getränke</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>18</v>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Red Bull 0,25</t>
+        </is>
+      </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Selgros</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kinder Riegel 21g</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Süßwaren</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>52</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Schwipp Schwapp 0,33l</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>36</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Kaufland</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Elf Bar Pot Blue Razz Lemonade</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Vape</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>14</v>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Elfbar Pod Blueberry 20mg 2x2ml</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Großhandel</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Elf Bar Pot Watermelon</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Vape</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>9</v>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Elfbar Pod Peach Ice 20mg 2x2ml</t>
+        </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Großhandel</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ELF BAR POTS Kiwi Passionfruit</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Vape</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>11</v>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Elfbar Pod Cherry 20mg 2x2ml</t>
+        </is>
+      </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Großhandel</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Elfbar Pot Cola</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Vape</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>6</v>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>48</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Elfbar Pod Watermelon 20mg 2x2ml</t>
+        </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Großhandel</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Elfbar Basisgerät</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Gesamt Stück</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>58</v>
+      </c>
+      <c r="E15" t="n">
+        <v>47</v>
+      </c>
+      <c r="F15" t="n">
+        <v>23</v>
+      </c>
+      <c r="G15" t="n">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
